--- a/Task-Migration/TransferData2/输入文件/task_info.xlsx
+++ b/Task-Migration/TransferData2/输入文件/task_info.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17280" windowHeight="7590" activeTab="2"/>
+    <workbookView windowWidth="17280" windowHeight="7590"/>
   </bookViews>
   <sheets>
     <sheet name="mysql2hive_01" sheetId="1" r:id="rId1"/>
@@ -29,14 +29,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="35">
+  <si>
+    <t>源名称</t>
+  </si>
+  <si>
+    <t>源表类型</t>
+  </si>
   <si>
     <t>源表表名</t>
   </si>
   <si>
-    <t>源表类型</t>
-  </si>
-  <si>
     <t>源表字段</t>
   </si>
   <si>
@@ -46,24 +49,30 @@
     <t>是否映射</t>
   </si>
   <si>
+    <t>目标名称</t>
+  </si>
+  <si>
+    <t>目标表类型</t>
+  </si>
+  <si>
     <t>目标表表名</t>
   </si>
   <si>
-    <t>目标表类型</t>
-  </si>
-  <si>
     <t>目标表字段</t>
   </si>
   <si>
     <t>目标表字段类型</t>
   </si>
   <si>
+    <t>zy_test_MYSQL</t>
+  </si>
+  <si>
+    <t>mysql</t>
+  </si>
+  <si>
     <t>students</t>
   </si>
   <si>
-    <t>mysql</t>
-  </si>
-  <si>
     <t>age</t>
   </si>
   <si>
@@ -73,6 +82,9 @@
     <t>是</t>
   </si>
   <si>
+    <t>zy_test_HADOOP</t>
+  </si>
+  <si>
     <t>hdfs</t>
   </si>
   <si>
@@ -112,7 +124,17 @@
     <t>null</t>
   </si>
   <si>
+    <t>sqlText</t>
+  </si>
+  <si>
     <t>select * from students</t>
+  </si>
+  <si>
+    <t>taskParams</t>
+  </si>
+  <si>
+    <t>spark.executor.cores=2
+spark.executor.memory=2g</t>
   </si>
 </sst>
 </file>
@@ -734,15 +756,21 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1269,149 +1297,179 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultColWidth="8.8421052631579" defaultRowHeight="14.1" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="14.6842105263158" customWidth="1"/>
-    <col min="2" max="3" width="13.1052631578947" customWidth="1"/>
-    <col min="4" max="4" width="12.9473684210526" customWidth="1"/>
-    <col min="5" max="5" width="12.1578947368421" customWidth="1"/>
-    <col min="6" max="6" width="11.8421052631579" customWidth="1"/>
-    <col min="7" max="8" width="11.4210526315789" customWidth="1"/>
-    <col min="9" max="9" width="16.0526315789474" customWidth="1"/>
+    <col min="1" max="1" width="14.5789473684211" customWidth="1"/>
+    <col min="3" max="3" width="14.6842105263158" customWidth="1"/>
+    <col min="4" max="4" width="13.1052631578947" customWidth="1"/>
+    <col min="5" max="5" width="12.9473684210526" customWidth="1"/>
+    <col min="6" max="6" width="12.1578947368421" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="8" max="8" width="12.1578947368421" customWidth="1"/>
+    <col min="9" max="9" width="11.8421052631579" customWidth="1"/>
+    <col min="10" max="10" width="11.4210526315789" customWidth="1"/>
+    <col min="11" max="11" width="16.0526315789474" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="1" t="s">
+    <row r="2" spans="1:11">
+      <c r="A2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="F2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1" t="s">
+    <row r="4" spans="1:11">
+      <c r="A4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="G4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="H4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="1" t="s">
+      <c r="J4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="1" t="s">
+      <c r="K4" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="F5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="I5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="E5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>18</v>
+      <c r="J5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1435,165 +1493,165 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="F1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
+      <c r="H1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="A2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="1" t="s">
+      <c r="E2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="A3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="A4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>12</v>
+      <c r="D4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="A5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>26</v>
+      <c r="C5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="E6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="1" t="s">
+      <c r="E6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="G6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1605,15 +1663,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.8421052631579" defaultRowHeight="14.1"/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultColWidth="8.8421052631579" defaultRowHeight="14.1" outlineLevelRow="1" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="34.3684210526316" customWidth="1"/>
+    <col min="1" max="1" width="17.4210526315789" customWidth="1"/>
+    <col min="2" max="2" width="34.3684210526316" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>27</v>
+        <v>31</v>
+      </c>
+      <c r="B1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" ht="28.2" spans="1:2">
+      <c r="A2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
